--- a/src/main/resources/doc/elevator.xlsx
+++ b/src/main/resources/doc/elevator.xlsx
@@ -224,21 +224,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -386,6 +373,18 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -761,7 +760,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -778,183 +777,184 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -962,27 +962,11 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="51">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
     <cellStyle name="货币" xfId="2" builtinId="4"/>
@@ -1032,6 +1016,8 @@
     <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 4" xfId="49"/>
+    <cellStyle name="常规 3" xfId="50"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -1056,11 +1042,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{ED92C178-530B-C46B-57CB-4C69AFBC150D}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{B9433531-1CA2-919F-8A1A-6C69199DAE40}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
   </tableStyles>
+  <colors>
+    <mruColors>
+      <color rgb="00FFFF00"/>
+      <color rgb="0000B0F0"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1356,378 +1348,213 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AM6"/>
-  <sheetFormatPr defaultColWidth="24.625" defaultRowHeight="30" customHeight="1" outlineLevelRow="5"/>
+  <dimension ref="A1:AM2"/>
+  <sheetFormatPr defaultColWidth="24.625" defaultRowHeight="30" customHeight="1" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="38.2115384615385" style="4" customWidth="1"/>
-    <col min="2" max="2" width="24.625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="47.6730769230769" style="5" customWidth="1"/>
-    <col min="4" max="4" width="40.1730769230769" style="5" customWidth="1"/>
-    <col min="5" max="5" width="24.625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="28.5673076923077" style="6" customWidth="1"/>
-    <col min="7" max="7" width="24.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="24.625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="27.1442307692308" style="5" customWidth="1"/>
-    <col min="10" max="10" width="24.625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="57.1346153846154" style="6" customWidth="1"/>
-    <col min="12" max="12" width="33.3942307692308" style="5" customWidth="1"/>
-    <col min="13" max="13" width="24.625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="26.7884615384615" style="6" customWidth="1"/>
-    <col min="15" max="15" width="24.625" style="6" customWidth="1"/>
-    <col min="16" max="16" width="45.8942307692308" style="6" customWidth="1"/>
-    <col min="17" max="17" width="42.3173076923077" style="6" customWidth="1"/>
-    <col min="18" max="18" width="28.3942307692308" style="6" customWidth="1"/>
-    <col min="19" max="21" width="24.625" style="6" customWidth="1"/>
-    <col min="22" max="22" width="61.9615384615385" style="4" customWidth="1"/>
-    <col min="23" max="23" width="56.9711538461538" style="6" customWidth="1"/>
-    <col min="24" max="24" width="57.8557692307692" style="6" customWidth="1"/>
-    <col min="25" max="25" width="24.625" style="5" customWidth="1"/>
-    <col min="26" max="26" width="60.5288461538462" style="6" customWidth="1"/>
-    <col min="27" max="27" width="24.625" style="6" customWidth="1"/>
-    <col min="28" max="28" width="27.1346153846154" style="6" customWidth="1"/>
-    <col min="29" max="36" width="24.625" style="6" customWidth="1"/>
-    <col min="37" max="38" width="24.625" style="7" customWidth="1"/>
-    <col min="39" max="39" width="24.625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="38.9326923076923" style="3" customWidth="1"/>
+    <col min="2" max="2" width="24.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="35.8846153846154" style="3" customWidth="1"/>
+    <col min="4" max="5" width="24.625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.5673076923077" style="3" customWidth="1"/>
+    <col min="7" max="7" width="40.375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="30.1826923076923" style="3" customWidth="1"/>
+    <col min="9" max="9" width="27.1442307692308" style="3" customWidth="1"/>
+    <col min="10" max="10" width="24.625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="36.5" style="3" customWidth="1"/>
+    <col min="12" max="13" width="24.625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="26.7884615384615" style="3" customWidth="1"/>
+    <col min="15" max="15" width="24.625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="31.25" style="3" customWidth="1"/>
+    <col min="17" max="18" width="30.7211538461538" style="3" customWidth="1"/>
+    <col min="19" max="21" width="24.625" style="3" customWidth="1"/>
+    <col min="22" max="22" width="42.75" style="3" customWidth="1"/>
+    <col min="23" max="23" width="43.2019230769231" style="3" customWidth="1"/>
+    <col min="24" max="24" width="48.3846153846154" style="4" customWidth="1"/>
+    <col min="25" max="25" width="24.625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="37.375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="24.625" style="3" customWidth="1"/>
+    <col min="28" max="28" width="27.1346153846154" style="3" customWidth="1"/>
+    <col min="29" max="30" width="24.625" style="3" customWidth="1"/>
+    <col min="31" max="31" width="33.75" style="3" customWidth="1"/>
+    <col min="32" max="36" width="24.625" style="3" customWidth="1"/>
+    <col min="37" max="38" width="24.625" style="5" customWidth="1"/>
+    <col min="39" max="39" width="24.625" style="6" customWidth="1"/>
     <col min="40" max="16384" width="24.625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:39">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="11" t="s">
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
+      <c r="Z1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="13"/>
-      <c r="AC1" s="10" t="s">
+      <c r="AA1" s="10"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10" t="s">
+      <c r="AD1" s="8"/>
+      <c r="AE1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="11" t="s">
+      <c r="AF1" s="8"/>
+      <c r="AG1" s="8"/>
+      <c r="AH1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="14" t="s">
+      <c r="AI1" s="10"/>
+      <c r="AJ1" s="11"/>
+      <c r="AK1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="15"/>
-      <c r="AM1" s="16"/>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="14"/>
     </row>
     <row r="2" s="2" customFormat="1" ht="66" customHeight="1" spans="1:39">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="K2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="L2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="M2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="20" t="s">
+      <c r="R2" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="19" t="s">
+      <c r="S2" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="T2" s="19" t="s">
+      <c r="T2" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="U2" s="19" t="s">
+      <c r="U2" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="V2" s="19" t="s">
+      <c r="V2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="W2" s="19" t="s">
+      <c r="W2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="19" t="s">
+      <c r="X2" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Y2" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="Z2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="AA2" s="19" t="s">
+      <c r="AA2" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="AB2" s="19" t="s">
+      <c r="AB2" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="AC2" s="19" t="s">
+      <c r="AC2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="AD2" s="19" t="s">
+      <c r="AD2" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="AE2" s="19" t="s">
+      <c r="AE2" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="AF2" s="19" t="s">
+      <c r="AF2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="AG2" s="19" t="s">
+      <c r="AG2" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="AH2" s="19" t="s">
+      <c r="AH2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="AI2" s="19" t="s">
+      <c r="AI2" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="AJ2" s="19" t="s">
+      <c r="AJ2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="AK2" s="19" t="s">
+      <c r="AK2" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="AL2" s="19" t="s">
+      <c r="AL2" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="AM2" s="19" t="s">
+      <c r="AM2" s="18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="3" s="3" customFormat="1" customHeight="1" spans="1:39">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="22"/>
-      <c r="Z3" s="23"/>
-      <c r="AA3" s="22"/>
-      <c r="AB3" s="22"/>
-      <c r="AC3" s="22"/>
-      <c r="AD3" s="22"/>
-      <c r="AE3" s="25"/>
-      <c r="AF3" s="25"/>
-      <c r="AG3" s="25"/>
-      <c r="AH3" s="22"/>
-      <c r="AI3" s="25"/>
-      <c r="AJ3" s="25"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="25"/>
-      <c r="AM3" s="27"/>
-    </row>
-    <row r="4" s="3" customFormat="1" customHeight="1" spans="1:39">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="21"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="25"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="21"/>
-      <c r="W4" s="23"/>
-      <c r="X4" s="23"/>
-      <c r="Y4" s="22"/>
-      <c r="Z4" s="23"/>
-      <c r="AA4" s="22"/>
-      <c r="AB4" s="22"/>
-      <c r="AC4" s="22"/>
-      <c r="AD4" s="22"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="25"/>
-      <c r="AG4" s="25"/>
-      <c r="AH4" s="22"/>
-      <c r="AI4" s="25"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="25"/>
-      <c r="AM4" s="27"/>
-    </row>
-    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:39">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="22"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="21"/>
-      <c r="W5" s="23"/>
-      <c r="X5" s="23"/>
-      <c r="Y5" s="22"/>
-      <c r="Z5" s="23"/>
-      <c r="AA5" s="22"/>
-      <c r="AB5" s="22"/>
-      <c r="AC5" s="22"/>
-      <c r="AD5" s="22"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="25"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="25"/>
-      <c r="AJ5" s="25"/>
-      <c r="AK5" s="25"/>
-      <c r="AL5" s="25"/>
-      <c r="AM5" s="27"/>
-    </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:39">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="21"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="22"/>
-      <c r="AB6" s="22"/>
-      <c r="AC6" s="22"/>
-      <c r="AD6" s="22"/>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="22"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="25"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="25"/>
-      <c r="AM6" s="27"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0"/>

--- a/src/main/resources/doc/elevator.xlsx
+++ b/src/main/resources/doc/elevator.xlsx
@@ -1042,7 +1042,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{B9433531-1CA2-919F-8A1A-6C69199DAE40}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{76E4604C-070B-8CF9-EE1E-C269B3FC495C}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
